--- a/src/pages/data/data_corp_demo.xlsx
+++ b/src/pages/data/data_corp_demo.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_AD4D2F04E46CFB4ACB3E20AB0D56E536693EDF2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C7F94A9-E369-4A73-BC39-2F3DE623AC89}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="11_AD4D2F04E46CFB4ACB3E20AB0D56E536693EDF2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F820510E-1EBB-4DC9-A6B7-73B649AE4CC8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_corp" sheetId="1" r:id="rId1"/>
     <sheet name="data_demo" sheetId="2" r:id="rId2"/>
+    <sheet name="data_mercado_media" sheetId="3" r:id="rId3"/>
+    <sheet name="data_mercado_basica" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="35">
   <si>
     <t>UNIDAD_ACADEMICA</t>
   </si>
@@ -107,6 +109,30 @@
   </si>
   <si>
     <t>RETENCION</t>
+  </si>
+  <si>
+    <t>MAT_CORPORACION</t>
+  </si>
+  <si>
+    <t>HC_PROVINCIA</t>
+  </si>
+  <si>
+    <t>TP_PROVINCIA</t>
+  </si>
+  <si>
+    <t>BASICAS_PROV</t>
+  </si>
+  <si>
+    <t>BÁSICA SAN FELIPE</t>
+  </si>
+  <si>
+    <t>PARV BÁSICA 1</t>
+  </si>
+  <si>
+    <t>PARV BÁSICA 2</t>
+  </si>
+  <si>
+    <t>PARV BÁSICA SAN FELIPE</t>
   </si>
 </sst>
 </file>
@@ -6147,4 +6173,774 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BBD637A-4294-4DD4-97BC-EA93107B05C7}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2020</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2">
+        <v>1176</v>
+      </c>
+      <c r="D2">
+        <v>2397</v>
+      </c>
+      <c r="E2">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2021</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3">
+        <v>1214</v>
+      </c>
+      <c r="D3">
+        <v>2338</v>
+      </c>
+      <c r="E3">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2022</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4">
+        <v>1226</v>
+      </c>
+      <c r="D4">
+        <v>2429</v>
+      </c>
+      <c r="E4">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2023</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5">
+        <v>1032</v>
+      </c>
+      <c r="D5">
+        <v>2553</v>
+      </c>
+      <c r="E5">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2024</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6">
+        <v>1086</v>
+      </c>
+      <c r="D6">
+        <v>2698</v>
+      </c>
+      <c r="E6">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2025</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7">
+        <v>1166</v>
+      </c>
+      <c r="D7">
+        <v>2706</v>
+      </c>
+      <c r="E7">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2020</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8">
+        <v>874</v>
+      </c>
+      <c r="D8">
+        <v>2800</v>
+      </c>
+      <c r="E8">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2021</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9">
+        <v>866</v>
+      </c>
+      <c r="D9">
+        <v>2926</v>
+      </c>
+      <c r="E9">
+        <v>2371</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2022</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10">
+        <v>889</v>
+      </c>
+      <c r="D10">
+        <v>2910</v>
+      </c>
+      <c r="E10">
+        <v>2457</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2023</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11">
+        <v>833</v>
+      </c>
+      <c r="D11">
+        <v>3088</v>
+      </c>
+      <c r="E11">
+        <v>2451</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2024</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12">
+        <v>811</v>
+      </c>
+      <c r="D12">
+        <v>3185</v>
+      </c>
+      <c r="E12">
+        <v>2548</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2025</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13">
+        <v>842</v>
+      </c>
+      <c r="D13">
+        <v>3375</v>
+      </c>
+      <c r="E13">
+        <v>2580</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D4E39ED-A2BA-4AF8-80FA-DB4BD0B334CE}">
+  <dimension ref="A1:D37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2020</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>764</v>
+      </c>
+      <c r="D2">
+        <v>6389</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2021</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>760</v>
+      </c>
+      <c r="D3">
+        <v>6434</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2022</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>753</v>
+      </c>
+      <c r="D4">
+        <v>6582</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2023</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>679</v>
+      </c>
+      <c r="D5">
+        <v>6465</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2024</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>590</v>
+      </c>
+      <c r="D6">
+        <v>6230</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2025</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>564</v>
+      </c>
+      <c r="D7">
+        <v>6074</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2020</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8">
+        <v>629</v>
+      </c>
+      <c r="D8">
+        <v>6389</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2021</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9">
+        <v>644</v>
+      </c>
+      <c r="D9">
+        <v>6434</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2022</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <v>628</v>
+      </c>
+      <c r="D10">
+        <v>6582</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2023</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11">
+        <v>580</v>
+      </c>
+      <c r="D11">
+        <v>6465</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2024</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12">
+        <v>569</v>
+      </c>
+      <c r="D12">
+        <v>6230</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2025</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13">
+        <v>555</v>
+      </c>
+      <c r="D13">
+        <v>6074</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2020</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14">
+        <v>1089</v>
+      </c>
+      <c r="D14">
+        <v>7797</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2021</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15">
+        <v>1075</v>
+      </c>
+      <c r="D15">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2022</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16">
+        <v>1031</v>
+      </c>
+      <c r="D16">
+        <v>7987</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2023</v>
+      </c>
+      <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17">
+        <v>989</v>
+      </c>
+      <c r="D17">
+        <v>7929</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2024</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18">
+        <v>937</v>
+      </c>
+      <c r="D18">
+        <v>7763</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2025</v>
+      </c>
+      <c r="B19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19">
+        <v>906</v>
+      </c>
+      <c r="D19">
+        <v>7720</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2020</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20">
+        <v>129</v>
+      </c>
+      <c r="D20">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2021</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21">
+        <v>96</v>
+      </c>
+      <c r="D21">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2022</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22">
+        <v>93</v>
+      </c>
+      <c r="D22">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2023</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23">
+        <v>67</v>
+      </c>
+      <c r="D23">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2024</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24">
+        <v>57</v>
+      </c>
+      <c r="D24">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2025</v>
+      </c>
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25">
+        <v>69</v>
+      </c>
+      <c r="D25">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2020</v>
+      </c>
+      <c r="B26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26">
+        <v>119</v>
+      </c>
+      <c r="D26">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2021</v>
+      </c>
+      <c r="B27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27">
+        <v>101</v>
+      </c>
+      <c r="D27">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2022</v>
+      </c>
+      <c r="B28" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28">
+        <v>95</v>
+      </c>
+      <c r="D28">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2023</v>
+      </c>
+      <c r="B29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29">
+        <v>70</v>
+      </c>
+      <c r="D29">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2024</v>
+      </c>
+      <c r="B30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30">
+        <v>81</v>
+      </c>
+      <c r="D30">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2025</v>
+      </c>
+      <c r="B31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31">
+        <v>85</v>
+      </c>
+      <c r="D31">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>2020</v>
+      </c>
+      <c r="B32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32">
+        <v>216</v>
+      </c>
+      <c r="D32">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>2021</v>
+      </c>
+      <c r="B33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33">
+        <v>170</v>
+      </c>
+      <c r="D33">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>2022</v>
+      </c>
+      <c r="B34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34">
+        <v>130</v>
+      </c>
+      <c r="D34">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>2023</v>
+      </c>
+      <c r="B35" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35">
+        <v>124</v>
+      </c>
+      <c r="D35">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>2024</v>
+      </c>
+      <c r="B36" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36">
+        <v>111</v>
+      </c>
+      <c r="D36">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>2025</v>
+      </c>
+      <c r="B37" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37">
+        <v>89</v>
+      </c>
+      <c r="D37">
+        <v>1052</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/pages/data/data_corp_demo.xlsx
+++ b/src/pages/data/data_corp_demo.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="11_AD4D2F04E46CFB4ACB3E20AB0D56E536693EDF2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F820510E-1EBB-4DC9-A6B7-73B649AE4CC8}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="11_AD4D2F04E46CFB4ACB3E20AB0D56E536693EDF2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2E3F1B5-88DB-4FEA-904A-3CA57D315EE7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_corp" sheetId="1" r:id="rId1"/>
     <sheet name="data_demo" sheetId="2" r:id="rId2"/>
     <sheet name="data_mercado_media" sheetId="3" r:id="rId3"/>
     <sheet name="data_mercado_basica" sheetId="4" r:id="rId4"/>
+    <sheet name="data_mercado_corp" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="37">
   <si>
     <t>UNIDAD_ACADEMICA</t>
   </si>
@@ -134,6 +135,12 @@
   <si>
     <t>PARV BÁSICA SAN FELIPE</t>
   </si>
+  <si>
+    <t>LOS ANDES</t>
+  </si>
+  <si>
+    <t>SAN FELIPE</t>
+  </si>
 </sst>
 </file>
 
@@ -168,8 +175,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6418,8 +6428,8 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6943,4 +6953,116 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11B2B74C-8410-4A88-84B6-55D375344D16}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>2020</v>
+      </c>
+      <c r="B2">
+        <v>4996</v>
+      </c>
+      <c r="C2">
+        <v>19381</v>
+      </c>
+      <c r="D2">
+        <v>14303</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2021</v>
+      </c>
+      <c r="B3">
+        <v>4926</v>
+      </c>
+      <c r="C3">
+        <v>19177</v>
+      </c>
+      <c r="D3">
+        <v>14436</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>2022</v>
+      </c>
+      <c r="B4">
+        <v>4845</v>
+      </c>
+      <c r="C4">
+        <v>19315</v>
+      </c>
+      <c r="D4">
+        <v>14591</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>2023</v>
+      </c>
+      <c r="B5">
+        <v>4374</v>
+      </c>
+      <c r="C5">
+        <v>19051</v>
+      </c>
+      <c r="D5">
+        <v>14646</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B6">
+        <v>4242</v>
+      </c>
+      <c r="C6">
+        <v>18593</v>
+      </c>
+      <c r="D6">
+        <v>14604</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B7">
+        <v>4276</v>
+      </c>
+      <c r="C7">
+        <v>18099</v>
+      </c>
+      <c r="D7">
+        <v>14727</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/pages/data/data_corp_demo.xlsx
+++ b/src/pages/data/data_corp_demo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="11_AD4D2F04E46CFB4ACB3E20AB0D56E536693EDF2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2E3F1B5-88DB-4FEA-904A-3CA57D315EE7}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="11_AD4D2F04E46CFB4ACB3E20AB0D56E536693EDF2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0535F28-D6D6-45C0-926B-101A933D1804}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_corp" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="data_mercado_media" sheetId="3" r:id="rId3"/>
     <sheet name="data_mercado_basica" sheetId="4" r:id="rId4"/>
     <sheet name="data_mercado_corp" sheetId="5" r:id="rId5"/>
+    <sheet name="data_sae_corp" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="40">
   <si>
     <t>UNIDAD_ACADEMICA</t>
   </si>
@@ -141,6 +142,15 @@
   <si>
     <t>SAN FELIPE</t>
   </si>
+  <si>
+    <t>POSTULANTES SAE</t>
+  </si>
+  <si>
+    <t>ADMITIDOS SAE</t>
+  </si>
+  <si>
+    <t>% ADMITIDOS</t>
+  </si>
 </sst>
 </file>
 
@@ -195,10 +205,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7065,4 +7071,463 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{482657F8-43FC-45F9-9834-57F8F380F1AB}">
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2021</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>188</v>
+      </c>
+      <c r="D2">
+        <v>81</v>
+      </c>
+      <c r="E2">
+        <v>0.43085106382978722</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2022</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>151</v>
+      </c>
+      <c r="D3">
+        <v>74</v>
+      </c>
+      <c r="E3">
+        <v>0.49006622516556292</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2023</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>162</v>
+      </c>
+      <c r="D4">
+        <v>80</v>
+      </c>
+      <c r="E4">
+        <v>0.49382716049382713</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2024</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>134</v>
+      </c>
+      <c r="D5">
+        <v>57</v>
+      </c>
+      <c r="E5">
+        <v>0.42537313432835822</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2025</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>137</v>
+      </c>
+      <c r="D6">
+        <v>61</v>
+      </c>
+      <c r="E6">
+        <v>0.44525547445255476</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2021</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7">
+        <v>141</v>
+      </c>
+      <c r="D7">
+        <v>87</v>
+      </c>
+      <c r="E7">
+        <v>0.61702127659574468</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2022</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8">
+        <v>116</v>
+      </c>
+      <c r="D8">
+        <v>58</v>
+      </c>
+      <c r="E8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2023</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9">
+        <v>128</v>
+      </c>
+      <c r="D9">
+        <v>81</v>
+      </c>
+      <c r="E9">
+        <v>0.6328125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2024</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <v>112</v>
+      </c>
+      <c r="D10">
+        <v>65</v>
+      </c>
+      <c r="E10">
+        <v>0.5803571428571429</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2025</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11">
+        <v>130</v>
+      </c>
+      <c r="D11">
+        <v>72</v>
+      </c>
+      <c r="E11">
+        <v>0.55384615384615388</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2021</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12">
+        <v>177</v>
+      </c>
+      <c r="D12">
+        <v>97</v>
+      </c>
+      <c r="E12">
+        <v>0.54802259887005644</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2022</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13">
+        <v>149</v>
+      </c>
+      <c r="D13">
+        <v>85</v>
+      </c>
+      <c r="E13">
+        <v>0.57046979865771807</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2023</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14">
+        <v>115</v>
+      </c>
+      <c r="D14">
+        <v>68</v>
+      </c>
+      <c r="E14">
+        <v>0.59130434782608698</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2024</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15">
+        <v>116</v>
+      </c>
+      <c r="D15">
+        <v>69</v>
+      </c>
+      <c r="E15">
+        <v>0.59482758620689657</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2025</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16">
+        <v>144</v>
+      </c>
+      <c r="D16">
+        <v>86</v>
+      </c>
+      <c r="E16">
+        <v>0.59722222222222221</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2021</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17">
+        <v>540</v>
+      </c>
+      <c r="D17">
+        <v>250</v>
+      </c>
+      <c r="E17">
+        <v>0.46296296296296297</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2022</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18">
+        <v>395</v>
+      </c>
+      <c r="D18">
+        <v>170</v>
+      </c>
+      <c r="E18">
+        <v>0.43037974683544306</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2023</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19">
+        <v>502</v>
+      </c>
+      <c r="D19">
+        <v>246</v>
+      </c>
+      <c r="E19">
+        <v>0.49003984063745021</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2024</v>
+      </c>
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20">
+        <v>548</v>
+      </c>
+      <c r="D20">
+        <v>274</v>
+      </c>
+      <c r="E20">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2025</v>
+      </c>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21">
+        <v>659</v>
+      </c>
+      <c r="D21">
+        <v>310</v>
+      </c>
+      <c r="E21">
+        <v>0.47040971168437024</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2021</v>
+      </c>
+      <c r="B22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22">
+        <v>303</v>
+      </c>
+      <c r="D22">
+        <v>124</v>
+      </c>
+      <c r="E22">
+        <v>0.40924092409240925</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2022</v>
+      </c>
+      <c r="B23" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23">
+        <v>263</v>
+      </c>
+      <c r="D23">
+        <v>117</v>
+      </c>
+      <c r="E23">
+        <v>0.44486692015209123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2023</v>
+      </c>
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24">
+        <v>260</v>
+      </c>
+      <c r="D24">
+        <v>99</v>
+      </c>
+      <c r="E24">
+        <v>0.38076923076923075</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2024</v>
+      </c>
+      <c r="B25" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25">
+        <v>263</v>
+      </c>
+      <c r="D25">
+        <v>96</v>
+      </c>
+      <c r="E25">
+        <v>0.36501901140684412</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2025</v>
+      </c>
+      <c r="B26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26">
+        <v>296</v>
+      </c>
+      <c r="D26">
+        <v>107</v>
+      </c>
+      <c r="E26">
+        <v>0.36148648648648651</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/pages/data/data_corp_demo.xlsx
+++ b/src/pages/data/data_corp_demo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="11_AD4D2F04E46CFB4ACB3E20AB0D56E536693EDF2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0535F28-D6D6-45C0-926B-101A933D1804}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="11_AD4D2F04E46CFB4ACB3E20AB0D56E536693EDF2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9CAA1D5-DF5F-4B78-A168-35F417847462}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_corp" sheetId="1" r:id="rId1"/>
@@ -5417,10 +5417,10 @@
         <v>324</v>
       </c>
       <c r="G190">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="H190">
-        <v>0</v>
+        <v>0.71707317073170729</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
@@ -5443,10 +5443,10 @@
         <v>270</v>
       </c>
       <c r="G191">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="H191">
-        <v>0</v>
+        <v>0.60396039603960394</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
@@ -5469,10 +5469,10 @@
         <v>221</v>
       </c>
       <c r="G192">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="H192">
-        <v>0</v>
+        <v>0.57948717948717954</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
@@ -5495,10 +5495,10 @@
         <v>308</v>
       </c>
       <c r="G193">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="H193">
-        <v>0</v>
+        <v>0.65865384615384615</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
@@ -5521,10 +5521,10 @@
         <v>347</v>
       </c>
       <c r="G194">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="H194">
-        <v>0</v>
+        <v>0.74603174603174605</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
@@ -5547,10 +5547,10 @@
         <v>407</v>
       </c>
       <c r="G195">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="H195">
-        <v>0</v>
+        <v>0.72826086956521741</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
@@ -6041,10 +6041,10 @@
         <v>212</v>
       </c>
       <c r="G214">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="H214">
-        <v>0</v>
+        <v>0.81927710843373502</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
@@ -6067,10 +6067,10 @@
         <v>236</v>
       </c>
       <c r="G215">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="H215">
-        <v>0</v>
+        <v>0.72131147540983598</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
@@ -6093,10 +6093,10 @@
         <v>175</v>
       </c>
       <c r="G216">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="H216">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
@@ -6119,10 +6119,10 @@
         <v>201</v>
       </c>
       <c r="G217">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="H217">
-        <v>0</v>
+        <v>0.648484848484848</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
@@ -6145,10 +6145,10 @@
         <v>208</v>
       </c>
       <c r="G218">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="H218">
-        <v>0</v>
+        <v>0.73291925465838503</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
@@ -6171,10 +6171,10 @@
         <v>255</v>
       </c>
       <c r="G219">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="H219">
-        <v>0</v>
+        <v>0.77464788732394396</v>
       </c>
     </row>
   </sheetData>
@@ -6197,7 +6197,8 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
